--- a/data_extactor/batch_10_fa/trimmed/batch_0010_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0010_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | مدیریت و امور اداری | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | ارتباطات و رسانه | مدیریت و اداره | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات پس از فروش و امور مشتریان | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | متصدیان ثبت سفارش | فروشندگان خرده‌فروشی | کارشناسان ارشد راهبرد بازاریابی موتورهای جستجو | خریداران عمده و خرده‌فروشی (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان خرده‌فروشی | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | پرسنلی و منابع انسانی | آموزش و تدریس | مهندسی و فناوری</t>
+          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | پرسنل و منابع انسانی | آموزش و پرورش | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بازرسان ساختمانی و ابنیه | مدیران مدیریت بحران و فوریت‌ها | سرپرستان رده‌اول نیروهای حراست و انتظامات | بازرسان و مأموران نظارت بر اماکن خاص | تحلیل‌گران امنیت اطلاعات | کارشناسان پیشگیری از سرقت و کسری کالا | مدیران حراست و امنیت</t>
+          <t>بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت بحران و پدافند غیرعامل | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | تحلیل‌گران امنیت اطلاعات | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | امور اداری و دفتری | رایانه و الکترونیک</t>
+          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان حسابداری، دفاتر مالی و حسابرسی | تحلیل‌گران بودجه | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | متصدیان محاسبات حقوق و دستمزد | مدیران خزانه‌داری و کنترلرهای مالی</t>
+          <t>کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان امور حقوق، دستمزد و ثبت زمان | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی</t>
+          <t>درک شفاهی | بینایی نزدیک | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان متره و برآورد هزینه | بازرسان و محققان اموال دولتی | کارشناسان ارزیابی خسارت بیمه خودرو | مدیران املاک، مستغلات و مجتمع‌های مسکونی | دلالان و کارگزاران املاک | ممیزان، وصول‌کنندگان و مأموران مالیاتی</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان برآورد هزینه و مترورها | بازرسان و ممیزان اموال دولتی | کارشناسان ارزیابی خسارت خودرو در شرکت‌های بیمه | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارگزاران و مدیران معاملات املاک | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ریاضیات | ساختمان و احداث ابنیه | اقتصاد و حسابداری | مدیریت و امور اداری | حقوق و مقررات دولتی | جغرافیا</t>
+          <t>ریاضیات | ساختمان و ساخت‌وساز | اقتصاد و حسابداری | مدیریت و اداره | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | بازرسان ساختمانی و ابنیه | کارشناسان متره و برآورد هزینه | مدیران املاک، مستغلات و مجتمع‌های مسکونی | دلالان و کارگزاران املاک | نقشه‌برداران | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارگزاران و مدیران معاملات املاک | مهندسان نقشه‌برداری | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | محاسبات عددی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | توانایی عددی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان حسابداری، دفاتر مالی و حسابرسی | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | تحلیل‌گران مدیریت و بهبود فرایندها | مدیران خزانه‌داری و کنترلرهای مالی</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | سخن گفتن | شنیدن فعال | ریاضیات | نگارش | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | سخن گفتن | گوش دادن فعال | ریاضیات | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | حقوق و مقررات دولتی | امور اداری و دفتری</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان بررسی و تصویب اعتبار | مشاوران اعتباری | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان تسهیلات و اعتبارات</t>
+          <t>حسابداران و حسابرسان | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | روش‌های علمی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تحلیل‌گران اعتبارات | اقتصاددانان | مدیران مالی | تحلیل‌گران کمی مالی | کارشناسان ریسک مالی | مدیران صندوق‌های سرمایه‌گذاری | مشاوران مالی فردی</t>
+          <t>تحلیل‌گران اعتبارات و تسهیلات | اقتصاددانان | مدیران امور مالی | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | مدیران صندوق‌های سرمایه‌گذاری | مشاوران مالی فردی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بیان کتبی | استدلال قیاسی | محاسبات عددی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بیان کتبی | استدلال قیاسی | توانایی عددی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تحلیل‌گران اعتبارات | مشاوران اعتباری | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تسهیلات و اعتبارات | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی</t>
+          <t>تحلیل‌گران اعتبارات و تسهیلات | مشاوران اعتباری و مدیریت بدهی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | فروش و بازاریابی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | ارزیابان، کارشناسان و محققان خسارت بیمه | تحلیل‌گران اعتبارات | کارشناسان ریسک مالی | کارمندان رسیدگی به خسارات و صدور بیمه‌نامه | کارشناسان فروش بیمه | کارشناسان تسهیلات و اعتبارات</t>
+          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان ریسک مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان و مسئولان تسهیلات و اعتبارات</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
